--- a/backend/data/ledger_weeks_62_84_template.xlsx
+++ b/backend/data/ledger_weeks_62_84_template.xlsx
@@ -398,19 +398,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K829"/>
-  <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="24.83203125" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" customWidth="1"/>
-    <col min="7" max="7" width="10.83203125" customWidth="1"/>
-    <col min="8" max="8" width="10.83203125" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" customWidth="1"/>
-    <col min="10" max="10" width="14.83203125" customWidth="1"/>
-    <col min="11" max="11" width="42.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -460,8 +447,8 @@
       <c r="D2" t="str">
         <v>Evans Ndungu</v>
       </c>
-      <c r="E2" t="str">
-        <v/>
+      <c r="E2">
+        <v>3000</v>
       </c>
       <c r="F2">
         <v>100</v>
@@ -472,11 +459,11 @@
       <c r="H2" t="str">
         <v/>
       </c>
-      <c r="I2" t="str">
-        <v/>
-      </c>
-      <c r="J2" t="str">
-        <v/>
+      <c r="I2">
+        <v>96500</v>
+      </c>
+      <c r="J2">
+        <v>99400</v>
       </c>
       <c r="K2" t="str">
         <v/>
@@ -495,8 +482,8 @@
       <c r="D3" t="str">
         <v>Patrick Njuguna</v>
       </c>
-      <c r="E3" t="str">
-        <v/>
+      <c r="E3">
+        <v>2000</v>
       </c>
       <c r="F3">
         <v>100</v>
@@ -507,11 +494,11 @@
       <c r="H3" t="str">
         <v/>
       </c>
-      <c r="I3" t="str">
-        <v/>
-      </c>
-      <c r="J3" t="str">
-        <v/>
+      <c r="I3">
+        <v>62900</v>
+      </c>
+      <c r="J3">
+        <v>64800</v>
       </c>
       <c r="K3" t="str">
         <v/>
@@ -530,8 +517,8 @@
       <c r="D4" t="str">
         <v>Benard Ngugi</v>
       </c>
-      <c r="E4" t="str">
-        <v/>
+      <c r="E4">
+        <v>2500</v>
       </c>
       <c r="F4">
         <v>100</v>
@@ -542,11 +529,11 @@
       <c r="H4" t="str">
         <v/>
       </c>
-      <c r="I4" t="str">
-        <v/>
-      </c>
-      <c r="J4" t="str">
-        <v/>
+      <c r="I4">
+        <v>84100</v>
+      </c>
+      <c r="J4">
+        <v>86500</v>
       </c>
       <c r="K4" t="str">
         <v/>
@@ -565,8 +552,8 @@
       <c r="D5" t="str">
         <v>Ndungu Mbugua</v>
       </c>
-      <c r="E5" t="str">
-        <v/>
+      <c r="E5">
+        <v>1500</v>
       </c>
       <c r="F5">
         <v>100</v>
@@ -577,11 +564,11 @@
       <c r="H5" t="str">
         <v/>
       </c>
-      <c r="I5" t="str">
-        <v/>
-      </c>
-      <c r="J5" t="str">
-        <v/>
+      <c r="I5">
+        <v>63750</v>
+      </c>
+      <c r="J5">
+        <v>65150</v>
       </c>
       <c r="K5" t="str">
         <v/>
@@ -601,7 +588,7 @@
         <v>Joseph Ndegwa</v>
       </c>
       <c r="E6" t="str">
-        <v/>
+        <v>NIL</v>
       </c>
       <c r="F6">
         <v>100</v>
@@ -612,11 +599,11 @@
       <c r="H6" t="str">
         <v/>
       </c>
-      <c r="I6" t="str">
-        <v/>
-      </c>
-      <c r="J6" t="str">
-        <v/>
+      <c r="I6">
+        <v>82900</v>
+      </c>
+      <c r="J6">
+        <v>82800</v>
       </c>
       <c r="K6" t="str">
         <v/>
@@ -636,7 +623,7 @@
         <v>Victor Kamau</v>
       </c>
       <c r="E7" t="str">
-        <v/>
+        <v>NIL</v>
       </c>
       <c r="F7">
         <v>100</v>
@@ -647,11 +634,11 @@
       <c r="H7" t="str">
         <v/>
       </c>
-      <c r="I7" t="str">
-        <v/>
-      </c>
-      <c r="J7" t="str">
-        <v/>
+      <c r="I7">
+        <v>90100</v>
+      </c>
+      <c r="J7">
+        <v>90000</v>
       </c>
       <c r="K7" t="str">
         <v/>
@@ -671,7 +658,7 @@
         <v>Peter Kimotho</v>
       </c>
       <c r="E8" t="str">
-        <v/>
+        <v>NIL</v>
       </c>
       <c r="F8">
         <v>100</v>
@@ -682,11 +669,11 @@
       <c r="H8" t="str">
         <v/>
       </c>
-      <c r="I8" t="str">
-        <v/>
-      </c>
-      <c r="J8" t="str">
-        <v/>
+      <c r="I8">
+        <v>66950</v>
+      </c>
+      <c r="J8">
+        <v>66850</v>
       </c>
       <c r="K8" t="str">
         <v/>
@@ -705,8 +692,8 @@
       <c r="D9" t="str">
         <v>Samson Mwangi</v>
       </c>
-      <c r="E9" t="str">
-        <v/>
+      <c r="E9">
+        <v>1500</v>
       </c>
       <c r="F9">
         <v>100</v>
@@ -717,11 +704,11 @@
       <c r="H9" t="str">
         <v/>
       </c>
-      <c r="I9" t="str">
-        <v/>
-      </c>
-      <c r="J9" t="str">
-        <v/>
+      <c r="I9">
+        <v>71550</v>
+      </c>
+      <c r="J9">
+        <v>72950</v>
       </c>
       <c r="K9" t="str">
         <v/>
@@ -740,8 +727,8 @@
       <c r="D10" t="str">
         <v>David Njoroge</v>
       </c>
-      <c r="E10" t="str">
-        <v/>
+      <c r="E10">
+        <v>1500</v>
       </c>
       <c r="F10">
         <v>100</v>
@@ -752,11 +739,11 @@
       <c r="H10" t="str">
         <v/>
       </c>
-      <c r="I10" t="str">
-        <v/>
-      </c>
-      <c r="J10" t="str">
-        <v/>
+      <c r="I10">
+        <v>69700</v>
+      </c>
+      <c r="J10">
+        <v>71100</v>
       </c>
       <c r="K10" t="str">
         <v/>
@@ -775,8 +762,8 @@
       <c r="D11" t="str">
         <v>John Gatimu</v>
       </c>
-      <c r="E11" t="str">
-        <v/>
+      <c r="E11">
+        <v>3000</v>
       </c>
       <c r="F11">
         <v>100</v>
@@ -787,14 +774,14 @@
       <c r="H11" t="str">
         <v/>
       </c>
-      <c r="I11" t="str">
-        <v/>
-      </c>
-      <c r="J11" t="str">
-        <v/>
+      <c r="I11">
+        <v>73200</v>
+      </c>
+      <c r="J11">
+        <v>76100</v>
       </c>
       <c r="K11" t="str">
-        <v/>
+        <v>Previous read as 73200 to reconcile with total on sheet (76100) — verify against book</v>
       </c>
     </row>
     <row r="12">
@@ -810,8 +797,8 @@
       <c r="D12" t="str">
         <v>Joel Ndungu</v>
       </c>
-      <c r="E12" t="str">
-        <v/>
+      <c r="E12">
+        <v>1500</v>
       </c>
       <c r="F12">
         <v>100</v>
@@ -822,11 +809,11 @@
       <c r="H12" t="str">
         <v/>
       </c>
-      <c r="I12" t="str">
-        <v/>
-      </c>
-      <c r="J12" t="str">
-        <v/>
+      <c r="I12">
+        <v>71400</v>
+      </c>
+      <c r="J12">
+        <v>72800</v>
       </c>
       <c r="K12" t="str">
         <v/>
@@ -845,8 +832,8 @@
       <c r="D13" t="str">
         <v>Benson Maina</v>
       </c>
-      <c r="E13" t="str">
-        <v/>
+      <c r="E13">
+        <v>1500</v>
       </c>
       <c r="F13">
         <v>100</v>
@@ -857,11 +844,11 @@
       <c r="H13" t="str">
         <v/>
       </c>
-      <c r="I13" t="str">
-        <v/>
-      </c>
-      <c r="J13" t="str">
-        <v/>
+      <c r="I13">
+        <v>71400</v>
+      </c>
+      <c r="J13">
+        <v>72800</v>
       </c>
       <c r="K13" t="str">
         <v/>
@@ -880,8 +867,8 @@
       <c r="D14" t="str">
         <v>Benson Kaniu</v>
       </c>
-      <c r="E14" t="str">
-        <v/>
+      <c r="E14">
+        <v>1590</v>
       </c>
       <c r="F14">
         <v>100</v>
@@ -892,14 +879,14 @@
       <c r="H14" t="str">
         <v/>
       </c>
-      <c r="I14" t="str">
-        <v/>
-      </c>
-      <c r="J14" t="str">
-        <v/>
+      <c r="I14">
+        <v>80320</v>
+      </c>
+      <c r="J14">
+        <v>81810</v>
       </c>
       <c r="K14" t="str">
-        <v/>
+        <v>Previous corrected to 80320 to reconcile with total on sheet — verify against book</v>
       </c>
     </row>
     <row r="15">
@@ -915,8 +902,8 @@
       <c r="D15" t="str">
         <v>Eustace Mugwanja</v>
       </c>
-      <c r="E15" t="str">
-        <v/>
+      <c r="E15">
+        <v>1500</v>
       </c>
       <c r="F15">
         <v>100</v>
@@ -927,11 +914,11 @@
       <c r="H15" t="str">
         <v/>
       </c>
-      <c r="I15" t="str">
-        <v/>
-      </c>
-      <c r="J15" t="str">
-        <v/>
+      <c r="I15">
+        <v>65850</v>
+      </c>
+      <c r="J15">
+        <v>67250</v>
       </c>
       <c r="K15" t="str">
         <v/>
@@ -950,8 +937,8 @@
       <c r="D16" t="str">
         <v>Joseph Gitonga</v>
       </c>
-      <c r="E16" t="str">
-        <v/>
+      <c r="E16">
+        <v>1500</v>
       </c>
       <c r="F16">
         <v>100</v>
@@ -962,11 +949,11 @@
       <c r="H16" t="str">
         <v/>
       </c>
-      <c r="I16" t="str">
-        <v/>
-      </c>
-      <c r="J16" t="str">
-        <v/>
+      <c r="I16">
+        <v>72500</v>
+      </c>
+      <c r="J16">
+        <v>73900</v>
       </c>
       <c r="K16" t="str">
         <v/>
@@ -985,8 +972,8 @@
       <c r="D17" t="str">
         <v>Wilson Kabichu</v>
       </c>
-      <c r="E17" t="str">
-        <v/>
+      <c r="E17">
+        <v>1500</v>
       </c>
       <c r="F17">
         <v>100</v>
@@ -997,11 +984,11 @@
       <c r="H17" t="str">
         <v/>
       </c>
-      <c r="I17" t="str">
-        <v/>
-      </c>
-      <c r="J17" t="str">
-        <v/>
+      <c r="I17">
+        <v>71900</v>
+      </c>
+      <c r="J17">
+        <v>73300</v>
       </c>
       <c r="K17" t="str">
         <v/>
@@ -1020,11 +1007,11 @@
       <c r="D18" t="str">
         <v>James Gachara</v>
       </c>
-      <c r="E18" t="str">
-        <v/>
+      <c r="E18">
+        <v>500</v>
       </c>
       <c r="F18">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1032,14 +1019,14 @@
       <c r="H18" t="str">
         <v/>
       </c>
-      <c r="I18" t="str">
-        <v/>
-      </c>
-      <c r="J18" t="str">
-        <v/>
+      <c r="I18">
+        <v>39900</v>
+      </c>
+      <c r="J18">
+        <v>40200</v>
       </c>
       <c r="K18" t="str">
-        <v/>
+        <v>Chai read as 200 to reconcile with total on sheet — verify against book</v>
       </c>
     </row>
     <row r="19">
@@ -1055,8 +1042,8 @@
       <c r="D19" t="str">
         <v>Erick Mwangi</v>
       </c>
-      <c r="E19" t="str">
-        <v/>
+      <c r="E19">
+        <v>1500</v>
       </c>
       <c r="F19">
         <v>100</v>
@@ -1067,11 +1054,11 @@
       <c r="H19" t="str">
         <v/>
       </c>
-      <c r="I19" t="str">
-        <v/>
-      </c>
-      <c r="J19" t="str">
-        <v/>
+      <c r="I19">
+        <v>62150</v>
+      </c>
+      <c r="J19">
+        <v>63550</v>
       </c>
       <c r="K19" t="str">
         <v/>
@@ -1091,7 +1078,7 @@
         <v>Erick Njogu</v>
       </c>
       <c r="E20" t="str">
-        <v/>
+        <v>NIL</v>
       </c>
       <c r="F20">
         <v>100</v>
@@ -1102,11 +1089,11 @@
       <c r="H20" t="str">
         <v/>
       </c>
-      <c r="I20" t="str">
-        <v/>
-      </c>
-      <c r="J20" t="str">
-        <v/>
+      <c r="I20">
+        <v>37600</v>
+      </c>
+      <c r="J20">
+        <v>37500</v>
       </c>
       <c r="K20" t="str">
         <v/>
@@ -1126,7 +1113,7 @@
         <v>Dennis Wasike</v>
       </c>
       <c r="E21" t="str">
-        <v/>
+        <v>NIL</v>
       </c>
       <c r="F21">
         <v>100</v>
@@ -1137,11 +1124,11 @@
       <c r="H21" t="str">
         <v/>
       </c>
-      <c r="I21" t="str">
-        <v/>
-      </c>
-      <c r="J21" t="str">
-        <v/>
+      <c r="I21">
+        <v>88150</v>
+      </c>
+      <c r="J21">
+        <v>88050</v>
       </c>
       <c r="K21" t="str">
         <v/>
@@ -1161,7 +1148,7 @@
         <v>Samuel Gachara</v>
       </c>
       <c r="E22" t="str">
-        <v/>
+        <v>NIL</v>
       </c>
       <c r="F22">
         <v>100</v>
@@ -1172,11 +1159,11 @@
       <c r="H22" t="str">
         <v/>
       </c>
-      <c r="I22" t="str">
-        <v/>
-      </c>
-      <c r="J22" t="str">
-        <v/>
+      <c r="I22">
+        <v>70600</v>
+      </c>
+      <c r="J22">
+        <v>70500</v>
       </c>
       <c r="K22" t="str">
         <v/>
@@ -1196,7 +1183,7 @@
         <v>Zabron Macharia</v>
       </c>
       <c r="E23" t="str">
-        <v/>
+        <v>NIL</v>
       </c>
       <c r="F23">
         <v>100</v>
@@ -1207,11 +1194,11 @@
       <c r="H23" t="str">
         <v/>
       </c>
-      <c r="I23" t="str">
-        <v/>
-      </c>
-      <c r="J23" t="str">
-        <v/>
+      <c r="I23">
+        <v>70500</v>
+      </c>
+      <c r="J23">
+        <v>70400</v>
       </c>
       <c r="K23" t="str">
         <v/>
@@ -1230,8 +1217,8 @@
       <c r="D24" t="str">
         <v>Paul Kimani</v>
       </c>
-      <c r="E24" t="str">
-        <v/>
+      <c r="E24">
+        <v>5000</v>
       </c>
       <c r="F24">
         <v>100</v>
@@ -1242,11 +1229,11 @@
       <c r="H24" t="str">
         <v/>
       </c>
-      <c r="I24" t="str">
-        <v/>
-      </c>
-      <c r="J24" t="str">
-        <v/>
+      <c r="I24">
+        <v>58600</v>
+      </c>
+      <c r="J24">
+        <v>63500</v>
       </c>
       <c r="K24" t="str">
         <v/>
@@ -1265,8 +1252,8 @@
       <c r="D25" t="str">
         <v>Dickson Karethi</v>
       </c>
-      <c r="E25" t="str">
-        <v/>
+      <c r="E25">
+        <v>3000</v>
       </c>
       <c r="F25">
         <v>100</v>
@@ -1277,11 +1264,11 @@
       <c r="H25" t="str">
         <v/>
       </c>
-      <c r="I25" t="str">
-        <v/>
-      </c>
-      <c r="J25" t="str">
-        <v/>
+      <c r="I25">
+        <v>65950</v>
+      </c>
+      <c r="J25">
+        <v>68850</v>
       </c>
       <c r="K25" t="str">
         <v/>
@@ -1300,8 +1287,8 @@
       <c r="D26" t="str">
         <v>Jackson Nakhulo</v>
       </c>
-      <c r="E26" t="str">
-        <v/>
+      <c r="E26">
+        <v>1500</v>
       </c>
       <c r="F26">
         <v>100</v>
@@ -1312,11 +1299,11 @@
       <c r="H26" t="str">
         <v/>
       </c>
-      <c r="I26" t="str">
-        <v/>
-      </c>
-      <c r="J26" t="str">
-        <v/>
+      <c r="I26">
+        <v>47000</v>
+      </c>
+      <c r="J26">
+        <v>48400</v>
       </c>
       <c r="K26" t="str">
         <v/>
@@ -1335,11 +1322,11 @@
       <c r="D27" t="str">
         <v>Isaiah Maina</v>
       </c>
-      <c r="E27" t="str">
-        <v/>
+      <c r="E27">
+        <v>40000</v>
       </c>
       <c r="F27">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1347,14 +1334,14 @@
       <c r="H27" t="str">
         <v/>
       </c>
-      <c r="I27" t="str">
-        <v/>
-      </c>
-      <c r="J27" t="str">
-        <v/>
+      <c r="I27">
+        <v>70250</v>
+      </c>
+      <c r="J27">
+        <v>110250</v>
       </c>
       <c r="K27" t="str">
-        <v/>
+        <v>Total on sheet implies no chai deducted this row — verify against book</v>
       </c>
     </row>
     <row r="28">
@@ -1371,7 +1358,7 @@
         <v>Harrison Kamau</v>
       </c>
       <c r="E28" t="str">
-        <v/>
+        <v>NIL</v>
       </c>
       <c r="F28">
         <v>100</v>
@@ -1382,11 +1369,11 @@
       <c r="H28" t="str">
         <v/>
       </c>
-      <c r="I28" t="str">
-        <v/>
-      </c>
-      <c r="J28" t="str">
-        <v/>
+      <c r="I28">
+        <v>74300</v>
+      </c>
+      <c r="J28">
+        <v>74200</v>
       </c>
       <c r="K28" t="str">
         <v/>
@@ -1406,7 +1393,7 @@
         <v>Stanly Gachara</v>
       </c>
       <c r="E29" t="str">
-        <v/>
+        <v>NIL</v>
       </c>
       <c r="F29">
         <v>100</v>
@@ -1417,11 +1404,11 @@
       <c r="H29" t="str">
         <v/>
       </c>
-      <c r="I29" t="str">
-        <v/>
-      </c>
-      <c r="J29" t="str">
-        <v/>
+      <c r="I29">
+        <v>23650</v>
+      </c>
+      <c r="J29">
+        <v>23550</v>
       </c>
       <c r="K29" t="str">
         <v/>
@@ -1440,8 +1427,8 @@
       <c r="D30" t="str">
         <v>George Ngechu</v>
       </c>
-      <c r="E30" t="str">
-        <v/>
+      <c r="E30">
+        <v>8600</v>
       </c>
       <c r="F30">
         <v>100</v>
@@ -1452,11 +1439,11 @@
       <c r="H30" t="str">
         <v/>
       </c>
-      <c r="I30" t="str">
-        <v/>
-      </c>
-      <c r="J30" t="str">
-        <v/>
+      <c r="I30">
+        <v>64300</v>
+      </c>
+      <c r="J30">
+        <v>72800</v>
       </c>
       <c r="K30" t="str">
         <v/>
@@ -1476,7 +1463,7 @@
         <v>Joshua Maina</v>
       </c>
       <c r="E31" t="str">
-        <v/>
+        <v>NIL</v>
       </c>
       <c r="F31">
         <v>100</v>
@@ -1487,11 +1474,11 @@
       <c r="H31" t="str">
         <v/>
       </c>
-      <c r="I31" t="str">
-        <v/>
-      </c>
-      <c r="J31" t="str">
-        <v/>
+      <c r="I31">
+        <v>92700</v>
+      </c>
+      <c r="J31">
+        <v>92600</v>
       </c>
       <c r="K31" t="str">
         <v/>
@@ -1510,8 +1497,8 @@
       <c r="D32" t="str">
         <v>Isaac Njenga</v>
       </c>
-      <c r="E32" t="str">
-        <v/>
+      <c r="E32">
+        <v>9000</v>
       </c>
       <c r="F32">
         <v>100</v>
@@ -1522,11 +1509,11 @@
       <c r="H32" t="str">
         <v/>
       </c>
-      <c r="I32" t="str">
-        <v/>
-      </c>
-      <c r="J32" t="str">
-        <v/>
+      <c r="I32">
+        <v>62400</v>
+      </c>
+      <c r="J32">
+        <v>71300</v>
       </c>
       <c r="K32" t="str">
         <v/>
@@ -1545,8 +1532,8 @@
       <c r="D33" t="str">
         <v>John Maina</v>
       </c>
-      <c r="E33" t="str">
-        <v/>
+      <c r="E33">
+        <v>2000</v>
       </c>
       <c r="F33">
         <v>100</v>
@@ -1557,11 +1544,11 @@
       <c r="H33" t="str">
         <v/>
       </c>
-      <c r="I33" t="str">
-        <v/>
-      </c>
-      <c r="J33" t="str">
-        <v/>
+      <c r="I33">
+        <v>68900</v>
+      </c>
+      <c r="J33">
+        <v>70800</v>
       </c>
       <c r="K33" t="str">
         <v/>
@@ -1580,8 +1567,8 @@
       <c r="D34" t="str">
         <v>Fines/Penalties</v>
       </c>
-      <c r="E34" t="str">
-        <v/>
+      <c r="E34">
+        <v>250</v>
       </c>
       <c r="F34" t="str">
         <v/>
@@ -1599,7 +1586,7 @@
         <v/>
       </c>
       <c r="K34" t="str">
-        <v/>
+        <v>Previous/total not transcribed — smaller text, verify against book</v>
       </c>
     </row>
     <row r="35">
@@ -1615,8 +1602,8 @@
       <c r="D35" t="str">
         <v>Tea Balance</v>
       </c>
-      <c r="E35" t="str">
-        <v/>
+      <c r="E35">
+        <v>1610</v>
       </c>
       <c r="F35" t="str">
         <v/>
@@ -1634,7 +1621,7 @@
         <v/>
       </c>
       <c r="K35" t="str">
-        <v/>
+        <v>Previous/total not transcribed — smaller text, verify against book</v>
       </c>
     </row>
     <row r="36">

--- a/backend/data/ledger_weeks_62_84_template.xlsx
+++ b/backend/data/ledger_weeks_62_84_template.xlsx
@@ -4,6 +4,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Ledger" sheetId="1" r:id="rId1"/>
+    <sheet name="Totals" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -29419,4 +29420,495 @@
     <ignoredError numberStoredAsText="1" sqref="A1:K829"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F24"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Week</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Date</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Contributions Collected</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Chai Collected</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Extra Collected</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Total Collected</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>62</v>
+      </c>
+      <c r="B2" t="str">
+        <v>2026-02-19</v>
+      </c>
+      <c r="C2">
+        <v>95190</v>
+      </c>
+      <c r="D2">
+        <v>3200</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>98390</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>63</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-02-26</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>3200</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>64</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-03-05</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>3200</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>65</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-03-12</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>3200</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>66</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-03-19</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>3200</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>67</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-03-26</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>3200</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>68</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-04-02</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>3200</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>69</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-04-09</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>3200</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>70</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-04-16</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>3200</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>71</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>3200</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>72</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-04-30</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>3200</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>73</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-05-07</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>3200</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>74</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-05-14</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>3200</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>75</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-05-21</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>3200</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>76</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-05-28</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>3200</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>77</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>3200</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>78</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-06-11</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>3200</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>79</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2026-06-18</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>3200</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>80</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2026-06-25</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>3200</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>81</v>
+      </c>
+      <c r="B21" t="str">
+        <v>2026-07-02</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>3200</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>82</v>
+      </c>
+      <c r="B22" t="str">
+        <v>2026-07-09</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>3200</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>83</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2026-07-16</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>3200</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>84</v>
+      </c>
+      <c r="B24" t="str">
+        <v>2026-07-23</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>3200</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>3200</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F24"/>
+  </ignoredErrors>
+</worksheet>
 </file>